--- a/MODELE SHAREPOINT VC.xlsx
+++ b/MODELE SHAREPOINT VC.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\AUTO\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686681C9-6699-4E34-8027-692D84C2C3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
+    <workbookView xWindow="30195" yWindow="1395" windowWidth="21600" windowHeight="11775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="101">
   <si>
     <t>DATE DE TRANSMISSION</t>
   </si>
@@ -34,38 +40,296 @@
     <t>PRENOM DU PROMOTEUR</t>
   </si>
   <si>
+    <t>CONTACT</t>
+  </si>
+  <si>
+    <t>NOM DU GESTIONNAIRE</t>
+  </si>
+  <si>
+    <t>PRENOM DU GESTIONNAIRE</t>
+  </si>
+  <si>
+    <t>SECTEUR D'ACTIVITE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPARTEMENT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILLE/COMMUNE </t>
+  </si>
+  <si>
+    <t>SITUATION  GEOGRAPHIQUE</t>
+  </si>
+  <si>
+    <t>NOM DU COMMERCIAL</t>
+  </si>
+  <si>
     <t>NUMERO ATTRIBUE</t>
   </si>
   <si>
-    <t>CONTACT</t>
-  </si>
-  <si>
-    <t>NOM DU GESTIONNAIRE</t>
-  </si>
-  <si>
-    <t>PRENOM DU GESTIONNAIRE</t>
-  </si>
-  <si>
-    <t>SECTEUR D'ACTIVITE</t>
-  </si>
-  <si>
-    <t>SITUATION  GEOGRAPHIQUE</t>
-  </si>
-  <si>
-    <t>NOM DU COMMERCIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEPARTEMENT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VILLE/COMMUNE </t>
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t>3ASCIF</t>
+  </si>
+  <si>
+    <t>ABAYA</t>
+  </si>
+  <si>
+    <t>AKOCHAYÉ ARSÈNE</t>
+  </si>
+  <si>
+    <t>2290194138888</t>
+  </si>
+  <si>
+    <t>Commerce</t>
+  </si>
+  <si>
+    <t>Atacora</t>
+  </si>
+  <si>
+    <t>Natitingou</t>
+  </si>
+  <si>
+    <t>Ourbouga</t>
+  </si>
+  <si>
+    <t>AWO Bernadin</t>
+  </si>
+  <si>
+    <t>ABDOUL TAYLOR</t>
+  </si>
+  <si>
+    <t>YESSOUFOU</t>
+  </si>
+  <si>
+    <t>ABDOUL LATIFOU</t>
+  </si>
+  <si>
+    <t>2290163625663</t>
+  </si>
+  <si>
+    <t>Achat et Vente des produits cosmetique</t>
+  </si>
+  <si>
+    <t>Mono</t>
+  </si>
+  <si>
+    <t>Lokossa</t>
+  </si>
+  <si>
+    <t>MONKPASEDJ</t>
+  </si>
+  <si>
+    <t>KAKPOVI Sebastien</t>
+  </si>
+  <si>
+    <t>ABIDELIASTORE OFFICIEL</t>
+  </si>
+  <si>
+    <t>DJOSSOU</t>
+  </si>
+  <si>
+    <t>DOUKPE JULIETTE</t>
+  </si>
+  <si>
+    <t>2290167305212</t>
+  </si>
+  <si>
+    <t>COMMERCE GENERAL</t>
+  </si>
+  <si>
+    <t>Atlantique</t>
+  </si>
+  <si>
+    <t>Abomey-Calavi</t>
+  </si>
+  <si>
+    <t>KPODJI-LES-MONTS</t>
+  </si>
+  <si>
+    <t>TAPE OLIVIER</t>
+  </si>
+  <si>
+    <t>AFFIMINTIN</t>
+  </si>
+  <si>
+    <t>GNANHOUI</t>
+  </si>
+  <si>
+    <t>CLAIRE</t>
+  </si>
+  <si>
+    <t>2290196851906</t>
+  </si>
+  <si>
+    <t>Zou</t>
+  </si>
+  <si>
+    <t>Bohicon</t>
+  </si>
+  <si>
+    <t>SOGBA</t>
+  </si>
+  <si>
+    <t>Bernard DOVONOU</t>
+  </si>
+  <si>
+    <t>AKODEGNON ET FILS</t>
+  </si>
+  <si>
+    <t>KODEGNON</t>
+  </si>
+  <si>
+    <t>MARC</t>
+  </si>
+  <si>
+    <t>2290165089247</t>
+  </si>
+  <si>
+    <t>ALIMENTATION GENERALE</t>
+  </si>
+  <si>
+    <t>Covè</t>
+  </si>
+  <si>
+    <t>DOME</t>
+  </si>
+  <si>
+    <t>ILLO Wabi Amadou</t>
+  </si>
+  <si>
+    <t>2290197366730</t>
+  </si>
+  <si>
+    <t>VOLI</t>
+  </si>
+  <si>
+    <t>ALLAO MIVA</t>
+  </si>
+  <si>
+    <t>LOLADE</t>
+  </si>
+  <si>
+    <t>ALEXANDRE</t>
+  </si>
+  <si>
+    <t>2290164753320</t>
+  </si>
+  <si>
+    <t>QUINCAILLERIE</t>
+  </si>
+  <si>
+    <t>AGNAGAN</t>
+  </si>
+  <si>
+    <t>AMLIHO</t>
+  </si>
+  <si>
+    <t>D. ARISTIDE</t>
+  </si>
+  <si>
+    <t>2290195347201</t>
+  </si>
+  <si>
+    <t>Za-Kpota</t>
+  </si>
+  <si>
+    <t>AGONGBO</t>
+  </si>
+  <si>
+    <t>ANASTHASIE SERVICES</t>
+  </si>
+  <si>
+    <t>AHOMAGNON</t>
+  </si>
+  <si>
+    <t>ANASTHASIE A K</t>
+  </si>
+  <si>
+    <t>2290195999467</t>
+  </si>
+  <si>
+    <t>Couffo</t>
+  </si>
+  <si>
+    <t>Toviklin</t>
+  </si>
+  <si>
+    <t>DAVI</t>
+  </si>
+  <si>
+    <t>TAGNON Ance</t>
+  </si>
+  <si>
+    <t>ARIKE DEEN STORE</t>
+  </si>
+  <si>
+    <t>DEEN</t>
+  </si>
+  <si>
+    <t>ZIKRATH ARIKÉ</t>
+  </si>
+  <si>
+    <t>2290197745077</t>
+  </si>
+  <si>
+    <t>ALEDJO</t>
+  </si>
+  <si>
+    <t>ARISCAR ET FILS</t>
+  </si>
+  <si>
+    <t>ARIGBO</t>
+  </si>
+  <si>
+    <t>SOUROU CARMELLE</t>
+  </si>
+  <si>
+    <t>2290190690633</t>
+  </si>
+  <si>
+    <t>Abomey</t>
+  </si>
+  <si>
+    <t>GBEKON</t>
+  </si>
+  <si>
+    <t>Atriki</t>
+  </si>
+  <si>
+    <t>GBEMANONZIN</t>
+  </si>
+  <si>
+    <t>2290166205569</t>
+  </si>
+  <si>
+    <t>AYIKPEVI SERVICE ET FILS</t>
+  </si>
+  <si>
+    <t>ASSOGBA</t>
+  </si>
+  <si>
+    <t>EMANUEL</t>
+  </si>
+  <si>
+    <t>2290166920945</t>
+  </si>
+  <si>
+    <t>HANGNAN</t>
+  </si>
+  <si>
+    <t>MOUZOUN Honoré</t>
+  </si>
+  <si>
+    <t>CEG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -149,6 +413,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,33 +725,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AI1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AI17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="1"/>
-    <col min="2" max="2" width="16.36328125" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" customWidth="1"/>
-    <col min="4" max="4" width="17.7265625" customWidth="1"/>
-    <col min="5" max="5" width="19.7265625" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
-    <col min="8" max="8" width="24.6328125" customWidth="1"/>
-    <col min="9" max="9" width="23.81640625" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" customWidth="1"/>
-    <col min="12" max="12" width="14.6328125" customWidth="1"/>
-    <col min="13" max="13" width="17.26953125" customWidth="1"/>
-    <col min="14" max="14" width="23.81640625" customWidth="1"/>
-    <col min="15" max="15" width="25.90625" customWidth="1"/>
-    <col min="16" max="16" width="18.90625" customWidth="1"/>
-    <col min="17" max="17" width="13.08984375" customWidth="1"/>
-    <col min="18" max="18" width="12.7265625" customWidth="1"/>
-    <col min="20" max="20" width="17.453125" customWidth="1"/>
-    <col min="21" max="21" width="12.453125" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="24.6640625" customWidth="1"/>
+    <col min="9" max="9" width="23.77734375" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="11" max="11" width="38.5546875" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="13" max="13" width="17.21875" customWidth="1"/>
+    <col min="14" max="14" width="23.77734375" customWidth="1"/>
+    <col min="15" max="15" width="25.88671875" customWidth="1"/>
+    <col min="16" max="16" width="18.88671875" customWidth="1"/>
+    <col min="17" max="17" width="13.109375" customWidth="1"/>
+    <col min="18" max="18" width="12.77734375" customWidth="1"/>
+    <col min="20" max="20" width="17.44140625" customWidth="1"/>
+    <col min="21" max="21" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="26">
+    <row r="1" spans="1:35" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,35 +770,35 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="Q1" s="4"/>
       <c r="R1" s="5"/>
@@ -549,6 +820,774 @@
       <c r="AH1" s="5"/>
       <c r="AI1" s="5"/>
     </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="6"/>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="8">
+        <v>2290163625663</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="6"/>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P4" s="6"/>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="P5" s="6"/>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P7" s="6"/>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P8" s="6"/>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="P17" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MODELE SHAREPOINT VC.xlsx
+++ b/MODELE SHAREPOINT VC.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI17"/>
+  <dimension ref="A1:AI139"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.109375" customWidth="1" min="1" max="1"/>
@@ -1784,6 +1784,9034 @@
       </c>
       <c r="P17" s="6" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>LA SOLUTION SIMPLE</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>AMOUSSOU</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>NOEL</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>2290197087661</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>AMOUSSOU</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>NOEL</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>2290197087661</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>PRESTATION DE SERVICE (TECHNICIEN)</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>SÈMÈ</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>DAGBEGNON JULIEN</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>LA TRINITE GSM</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>N'SOUGAN</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>PAULIN</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>2290167634393</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>N'SOUGAN</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>PAULIN</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>2290167634393</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>KPOGUETOMEY</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>KPOGUETOMEY</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>LA TRINITE GSM</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>N'SOUGAN</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>PAULIN</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>2290167634393</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>N'SOUGAN</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>PAULIN</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>2290167634393</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>MONO</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>COMÈ</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>COME</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>LA TRINITE GSM</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>N'SOUGAN</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>PAULIN</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>2290167634393</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>N'SOUGAN</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>PAULIN</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>2290167634393</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>ATTOTINGA</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>ATTOTINGA</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>LAVODIE</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>AWITI</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>ROGATIEN</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>2290195251801</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>AWITI</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>ROGATIEN</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>2290195251801</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>VENTE DE FOURNITURE SCOLAIRE</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>ALLADA</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>ADSADJI</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>AGBOZO GHISLAIN</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>LAVODIE</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>AWITI</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>ROGATIEN</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>2290195251801</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>AWITI</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>ROGATIEN</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>2290195251801</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>MENUISERIE</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>ALLADA</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>LISSEGAZOUN</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>AGBOZO GHISLAIN</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>LE MENU</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>ADOGBA</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>FRANÇOIS D'ASISE</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>2290196100789</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>ADOGBA</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>FRANÇOIS D'ASISE</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>2290196100789</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>CENTRE DE LOISIRS</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>AGASSA-GODOMEY</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>TAPE OLIVIER</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>LE RABBI . JC</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>N'GAYE</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>FIACRE HUBERT</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>2290197252896</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>N'GAYE</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>FIACRE HUBERT</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>2290197252896</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>PRODUITS GSM</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>ZOUNZONME</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>LE SILENCE DE DIEU</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>LAWSON</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>KOUDAHIN MESSAN</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>2290198133389</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>LAWSON</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>KOUDAHIN MESSAN</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>2290198133389</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>POISSONNERIE</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>DOVO</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>DOVO</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>LE SILENCE DE DIEU</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>LAWSON</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>KOUDAHIN MESSAN</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>2290198133389</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>LAWSON</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>KOUDAHIN MESSAN</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>2290198133389</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>POISSONNERIE</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>SÈMÈ-KPODJI</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>KPODJI</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>LE SILENCE DE DIEU</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>LAWSON</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>KOUDAHIN MESSAN</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>2290198133389</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>LAWSON</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>KOUDAHIN MESSAN</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>2290198133389</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>POISSONNERIE</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>AYAME</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>AYAME</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>LES ANGES ADONAI DE OSK</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>KPADONOU</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>OUSSOU SEBASTIEN</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>2290196298476</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>KPADONOU</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>OUSSOU SEBASTIEN</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>2290196298476</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL ET DIVE</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>KPOSSIDJA</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>CHICOTO EVRARD</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>LES ELUS DE L'ETERNEL</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>VIHINSO</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>PATRICE</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>2290166160201</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>VIHINSO</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>PATRICE</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>2290166160201</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>QUINCAILLERIE</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>ZOCA</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>DAGBEGNON JULIEN</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>LIANO KANO</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>AKAKPO</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>AFISSOU</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>2290166772205</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>AKAKPO</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>AFISSOU</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>2290166772205</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>SOGBA</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>LEGITIME</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>TOHOUIGNAN MASSO</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>LETONDE JUDITH</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>2290194222490</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>TOHOUIGNAN MASSO</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>LETONDE JUDITH</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>2290194222490</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>IMPRIMERIE</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>ZOCA</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>DAGBEGNON JULIEN</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>MAGIQUE ELECTRO</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>ALLEDAHOUN AVANON</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>DOUKPO HERVÉ</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>2290195421736</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>ALLEDAHOUN AVANON</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>DOUKPO HERVÉ</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>2290195421736</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>SANCON</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>MARXSORFTSERVICES</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>MARCELLIN</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>DOSSOU</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>2290195120207</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>MARCELLIN</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>DOSSOU</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>2290195120207</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>VENTE EN LIGNE</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>ATAKPOCODJI</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>SALOMON QUENUM</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>MASSAOUDOU ET FILS</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>SIDO</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>MASSAOUDOU</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>2290148583861</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>SIDO</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>MASSAOUDOU</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>2290148583861</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>ALIMENTATION GÉNÉRALE</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>KÉROU</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>KEROU</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>MATH CHIK</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>HOUNSOUNOU</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>GBAHUNDE MATHIAS</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>2290160654064</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>HOUNSOUNOU</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>GBAHUNDE MATHIAS</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>2290160654064</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>KINZOUN</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>KINZOUN</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>MATH CHIK</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>HOUNSOUNOU</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>GBAHUNDE MATHIAS</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>2290160654064</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>HOUNSOUNOU</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>GBAHUNDE MATHIAS</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>2290160654064</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>AYOU</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>SEBO</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>MERVY PLUS</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>TAPE</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>MERVEILLE</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>2290167453758</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>TAPE</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>MERVEILLE</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>2290167453758</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>MAGASIN SPECIALISE DE TEXTILES</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>ADJAGBO</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>CHICOTO EVRARD</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>MOULDAG</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>DAGA</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>MOULICATH</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>2290196491513</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>DAGA</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>MOULICATH</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>2290196491513</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>CENTRE COMMERCIAUX D'INFORMATIQUE</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>AKASSATO CENTRE</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>TAPE OLIVIER</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>MOUNTAIN CITY</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>HOUNYE</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>DOSSOU ROMARIC</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>2290196546805</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>HOUNYE</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>DOSSOU ROMARIC</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>2290196546805</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GÉNÉRAL</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>KPOSSIDJA</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>SALIGA THIERIE</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>NASCO JIAOU CHRISTVI</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>AMOUSSOU</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>MEDIANE JIAOU</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>2290167376186</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>AMOUSSOU</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>MEDIANE JIAOU</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>2290167376186</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>ALIMENTATION GENERAL</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>DOSSOUNOU</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>SOUNOUVOU FLORENT</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>NKP VICTOR HLS ET FILS AHDJN</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>AHOUANDJINOU</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>NOUKPO VICTOR</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>2290169120521</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>AHOUANDJINOU</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>NOUKPO VICTOR</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>2290169120521</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>QUINCALLERIE</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>ZOUNGO</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>SOUNOUVOU FLORENT</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>NOUMANKE ET FILS</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>FASSINOU</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>JEAN-CLAUDE</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>2290162076708</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>FASSINOU</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>JEAN-CLAUDE</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>2290162076708</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>ADJOHOUN</t>
+        </is>
+      </c>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>ADJAHO</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>NOUMANKE ET FILS</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>FASSINOU</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>JEAN-CLAUDE</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>2290162076708</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>FASSINOU</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>JEAN-CLAUDE</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>2290162076708</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>AGAGA</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>AGAGA</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>O'FINDRIVE MULTI SERVICES</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>D'ALMEIDA</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>FRANCK BORIS</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>2290165678191</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>D'ALMEIDA</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>FRANCK BORIS</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>2290165678191</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>KPATALOKOLI</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>ORTON ET FILS</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>ATIYE</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>RUSTIQUE PENARDO</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>2290162811397</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>ATIYE</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>RUSTIQUE PENARDO</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>2290162811397</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>BTP</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>SOGBA</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>PHARMACIE CITE DE PAIX</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>AMOUSSOU</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>YÉHOUEGNON LOUIS</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>2290160225562</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>AMOUSSOU</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>YÉHOUEGNON LOUIS</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>2290160225562</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>PHARMACIE</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>TOFFO</t>
+        </is>
+      </c>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>HOUEGBO-GARE</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>PHARMACIE CITE DE PAIX</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>AMOUSSOU</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>YÉHOUEGNON LOUIS</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>2290160225562</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>AMOUSSOU</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>YÉHOUEGNON LOUIS</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>2290160225562</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>PHARMACIE</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>AGONME</t>
+        </is>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>AGONME</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>PIERRE LA LUMIERE DE DIEU</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>HOUNKANRIN</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>MAHUNOU</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>2290194300565</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>HOUNKANRIN</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>MAHUNOU</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>2290194300565</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>CENTRES DE FORMATION</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>AKOSSAVIE</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>SOUNOUVOU FLORENT</t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>RADEX PHOTO PLUS</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>OGOUDJOBI</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>RACHIDI</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>2290195208753</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>OGOUDJOBI</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>RACHIDI</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>2290195208753</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>COVÈ</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>ZANTAN</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>RANKHACY ET FRERES</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>YOCLOUNON</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>BODELAIS</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>2290144434579</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>YOCLOUNON</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>BODELAIS</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>2290144434579</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>ACHAT ET VENTE DE PRODUITS GSM</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>FIFONSI</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="inlineStr">
+        <is>
+          <t>CHICOTO EVRARD</t>
+        </is>
+      </c>
+      <c r="P51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>ROSASHOP PLUS</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>NONTONDJI</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>ROSE HOUEVI</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>2290143513902</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>NONTONDJI</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>ROSE HOUEVI</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>2290143513902</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>MERCERIES</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>ALANSAKOME</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>CHICOTO EVRARD</t>
+        </is>
+      </c>
+      <c r="P52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>SACREE PUISSANCE DIVINE</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>ZOUNNON</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>GBENOUKPO ELIE VENCESLAS</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>2290164112922</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>ZOUNNON</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>GBENOUKPO ELIE VENCESLAS</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>2290164112922</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>FOURNITURE SCOLAIRE</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>COVÈ</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>HOUNDO</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>SADONAGNON ET FILS</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>SADONAGNON</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>COHOVI</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>2290195344464</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>SADONAGNON</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>COHOVI</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>2290195344464</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>YEKON DO</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
+          <t>AGNAN RAOUL</t>
+        </is>
+      </c>
+      <c r="P54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>SADONAGNON ET FILS</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>SADONAGNON</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>COHOVI</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>2290195344464</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>SADONAGNON</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>COHOVI</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>2290195344464</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>YEKON DO</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="inlineStr">
+        <is>
+          <t>AGNAN RAOUL</t>
+        </is>
+      </c>
+      <c r="P55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>SAGJ GSM PRO</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>SODJO ALLADASSI</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>GILDAS JULES</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>2290197256172</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>SODJO ALLADASSI</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>GILDAS JULES</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>2290197256172</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>VENTE DE CIMENT</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>TOFFO</t>
+        </is>
+      </c>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>HOUEGBO</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>SAGJ GSM PRO</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>SODJO ALLADASSI</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>GILDAS JULES</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>2290197256172</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>SODJO ALLADASSI</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>GILDAS JULES</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>2290197256172</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>VENTE DE CIMENT</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>AGBAME</t>
+        </is>
+      </c>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>AGBAME</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>SAGJ GSM PRO</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>SODJO ALLADASSI</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>GILDAS JULES</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>2290197256172</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>SODJO ALLADASSI</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>GILDAS JULES</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>2290197256172</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>VENTE DE CIMENT</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t>GUEME</t>
+        </is>
+      </c>
+      <c r="N58" s="6" t="inlineStr">
+        <is>
+          <t>GUEME</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>SAINT HAROLD BUSINESS</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>SOSSOU</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>BLAISE OBED HAROLD CYRIANOS</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>2290196600840</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>SOSSOU</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>BLAISE OBED HAROLD CYRIANOS</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>2290196600840</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>COUFFO</t>
+        </is>
+      </c>
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>DOGBO</t>
+        </is>
+      </c>
+      <c r="N59" s="6" t="inlineStr">
+        <is>
+          <t>TOTA</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="inlineStr">
+        <is>
+          <t>TAGNON ANCE</t>
+        </is>
+      </c>
+      <c r="P59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>SAINT MICHEL LE LEADER</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>ADJOVI</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>COLOMBE JUDITH</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>2290194461056</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>ADJOVI</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>COLOMBE JUDITH</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>2290194461056</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t>ZAGNANADO</t>
+        </is>
+      </c>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>CENTRE</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>SAINT RAPHAEL LUMIERE SERVICE PLUS</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>GOUNMANBOU</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>MAHOULI NESTOR</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>2290165506763</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>GOUNMANBOU</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>MAHOULI NESTOR</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>2290165506763</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="inlineStr">
+        <is>
+          <t>ALLADA</t>
+        </is>
+      </c>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>AGON</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>SAINT SYLVESTRE ET SHOP</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>MAGNON FINON</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>SYLVESTRE</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>2290161622328</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>MAGNON FINON</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>SYLVESTRE</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>2290161622328</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>PRET A PORTER</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY</t>
+        </is>
+      </c>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>SOGBO-ALIHO</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>SAINTE VIERGE MARIE NOTRE MERE</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>KOUVIDEKOU</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>FREJUSTE</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>2290196930455</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>KOUVIDEKOU</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>FREJUSTE</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>2290196930455</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>PAPETERIE</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>TORI CADA</t>
+        </is>
+      </c>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>ZOUNVESSEHOU</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="inlineStr">
+        <is>
+          <t>AGBOZO GHISLAIN</t>
+        </is>
+      </c>
+      <c r="P63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>SAM LEGENDE</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>GNANSOUNOU</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>SAMUEL MONDOUKPE</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>2290194329273</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>GNANSOUNOU</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>SAMUEL MONDOUKPE</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>2290194329273</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>COUFFO</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>LALO</t>
+        </is>
+      </c>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>CENTRE</t>
+        </is>
+      </c>
+      <c r="O64" s="6" t="inlineStr">
+        <is>
+          <t>TAGNON ANCE</t>
+        </is>
+      </c>
+      <c r="P64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>SEGNIDON ET FILS</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>SAINOU</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>AISSI FIACRE</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>2290167801513</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>SAINOU</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>AISSI FIACRE</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>2290167801513</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>TOFFO</t>
+        </is>
+      </c>
+      <c r="N65" s="6" t="inlineStr">
+        <is>
+          <t>HOUEGBO</t>
+        </is>
+      </c>
+      <c r="O65" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>SEGNIDON ET FILS</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>SAINOU</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>AISSI FIACRE</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>2290167801513</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>SAINOU</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>AISSI FIACRE</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>2290167801513</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>ALLADA</t>
+        </is>
+      </c>
+      <c r="N66" s="6" t="inlineStr">
+        <is>
+          <t>AGON</t>
+        </is>
+      </c>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>SEJOS GRACE</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>SOIGBE</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>ETIENNE GILDAS</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>2290195410798</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>SOIGBE</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>ETIENNE GILDAS</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>2290195410798</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>TOFFO</t>
+        </is>
+      </c>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>HOUETO</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="inlineStr">
+        <is>
+          <t>TAPE OLIVIER</t>
+        </is>
+      </c>
+      <c r="P67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>SEMEVO LA VERITE</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>AGBON</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>SEMEVO STANISLAS</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>2290165033524</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>AGBON</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>SEMEVO STANISLAS</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>2290165033524</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>COUFFO</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>LALO</t>
+        </is>
+      </c>
+      <c r="N68" s="6" t="inlineStr">
+        <is>
+          <t>CENTRE</t>
+        </is>
+      </c>
+      <c r="O68" s="6" t="inlineStr">
+        <is>
+          <t>TAGNON ANCE</t>
+        </is>
+      </c>
+      <c r="P68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>SINOU ET FILS</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>SINOU</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>MAHUGNON AMBROISE</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>2290166984172</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>SINOU</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>MAHUGNON AMBROISE</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>2290166984172</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>COVÈ</t>
+        </is>
+      </c>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>AHITO</t>
+        </is>
+      </c>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>SOCLE DE LA GESTION IMMOBILIERE</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>DOSSOU</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>CONSTANT</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>2290161575024</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>DOSSOU</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>CONSTANT</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>2290161575024</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>GESTION IMMOBILIÈRE</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N70" s="6" t="inlineStr">
+        <is>
+          <t>TOKSA ZOUNJO</t>
+        </is>
+      </c>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>DAGBEGNON JULIEN</t>
+        </is>
+      </c>
+      <c r="P70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>SOTODJIOKE</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>SOTODJI OKE</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>EMMANUEL</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>2290152005272</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>SOTODJI OKE</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>EMMANUEL</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>2290152005272</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>DIVERS</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>OUIDAH</t>
+        </is>
+      </c>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>HOUE</t>
+        </is>
+      </c>
+      <c r="O71" s="6" t="inlineStr">
+        <is>
+          <t>AGBOZO GHISLAIN</t>
+        </is>
+      </c>
+      <c r="P71" s="6" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>STELLA JESUKPE ET FILS</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>AGOSSOU</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>MIRACLETTE CHRISTGIRL JESUKPE</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>2290155137767</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>AGOSSOU</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>MIRACLETTE CHRISTGIRL JESUKPE</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>2290155137767</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>AGROALIMENTAIRE</t>
+        </is>
+      </c>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N72" s="6" t="inlineStr">
+        <is>
+          <t>COCOCODJI</t>
+        </is>
+      </c>
+      <c r="O72" s="6" t="inlineStr">
+        <is>
+          <t>SOUNOUVOU FLORENT</t>
+        </is>
+      </c>
+      <c r="P72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>SYLVIA ET FILS</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>HOUETCHENOU</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>FLORIANE SYLVIA</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>2290190075616</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>HOUETCHENOU</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>FLORIANE SYLVIA</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>2290190075616</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>QUINCAILLERIE</t>
+        </is>
+      </c>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M73" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N73" s="6" t="inlineStr">
+        <is>
+          <t>SOGBA</t>
+        </is>
+      </c>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>SENATEUR ET KOUNDE</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>GOUSSI</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>GILDAS MAHOUNOU MARCELLIN</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>2290196065925</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>GOUSSI</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>GILDAS MAHOUNOU MARCELLIN</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>2290196065925</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>GESTION IMMOBILIÈRE</t>
+        </is>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>DOSSITO</t>
+        </is>
+      </c>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="O74" s="6" t="inlineStr">
+        <is>
+          <t>AGBOZO GHISLAIN</t>
+        </is>
+      </c>
+      <c r="P74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>TADAGBE SERVICE PLUS</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>NIELO</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>COSSI JÉRÉMIE</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>2290197753579</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>NIELO</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>COSSI JÉRÉMIE</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>2290197753579</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>COMPLEMENTS ALIMENTAIRES</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>AKOSSAVIE</t>
+        </is>
+      </c>
+      <c r="O75" s="6" t="inlineStr">
+        <is>
+          <t>SOUNOUVOU FLORENT</t>
+        </is>
+      </c>
+      <c r="P75" s="6" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>TAGER ET FILS</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>TAPE</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>GÉRARD</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>2290167538440</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>TAPE</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>GÉRARD</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>2290167538440</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>TANKPE</t>
+        </is>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>TAPE OLIVIER</t>
+        </is>
+      </c>
+      <c r="P76" s="6" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>TIANGA BUSINESS CENTER</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>YOA</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>TIANGA GRACE</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>2290198140201</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>YOA</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>TIANGA GRACE</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>2290198140201</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>ZOGBADJE</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="inlineStr">
+        <is>
+          <t>MELE PRINCE</t>
+        </is>
+      </c>
+      <c r="P77" s="6" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>TSUROLAMIM</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>ADANKPO</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>CODJO MOÏSE</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>2290196181617</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>ADANKPO</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>CODJO MOÏSE</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>2290196181617</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY</t>
+        </is>
+      </c>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>DJEGBE</t>
+        </is>
+      </c>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>YEGNIMI DIVINE</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>FAGLA</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>YEGNIMI MARIETTE</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>2290151111348</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>FAGLA</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>YEGNIMI MARIETTE</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>2290151111348</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>BIJOUTERIE-JOAILLERIE</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>COCOCODJI</t>
+        </is>
+      </c>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>SOUNOUVOU FLORENT</t>
+        </is>
+      </c>
+      <c r="P79" s="6" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>YEYINOU VALORISATION</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>HOUNNOU</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>JEAN</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>2290198808324</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>HOUNNOU</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>JEAN</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>2290198808324</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>QUINCAILLERIE ET COUTURE / COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N80" s="6" t="inlineStr">
+        <is>
+          <t>GLEGBODJI</t>
+        </is>
+      </c>
+      <c r="O80" s="6" t="inlineStr">
+        <is>
+          <t>AGNAN RAOUL</t>
+        </is>
+      </c>
+      <c r="P80" s="6" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>YRIEL SERVICE INFORMATIK</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>SOSSOU</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>KOMLAN ROBERT</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>2290163231566</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>SOSSOU</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>KOMLAN ROBERT</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>2290163231566</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL / CONSOMMABLE INFORMATIK</t>
+        </is>
+      </c>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N81" s="6" t="inlineStr">
+        <is>
+          <t>GLEGBODJI DO</t>
+        </is>
+      </c>
+      <c r="O81" s="6" t="inlineStr">
+        <is>
+          <t>AGNAN RAOUL</t>
+        </is>
+      </c>
+      <c r="P81" s="6" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>ZANKPE ET FILS</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>ZANKPE</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>DOGNON FERIOLE</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>2290157888662</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>ZANKPE</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>DOGNON FERIOLE</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>2290157888662</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>TANGUIÉTA</t>
+        </is>
+      </c>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>YANKA</t>
+        </is>
+      </c>
+      <c r="O82" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P82" s="6" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>ZOCA-LOCA</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>AYOSSO</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>LÉANDRE CONSTANT COOMLAN</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>2290197165234</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>AYOSSO</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>LÉANDRE CONSTANT COOMLAN</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>2290197165234</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>BAR RESTAURANT</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>ZOCA</t>
+        </is>
+      </c>
+      <c r="O83" s="6" t="inlineStr">
+        <is>
+          <t>DAGBEGNON JULIEN</t>
+        </is>
+      </c>
+      <c r="P83" s="6" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>ZONA ROLD</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>AZON</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>PASTEL ROLANDO</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>2290166335562</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>AZON</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>PASTEL ROLANDO</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>2290166335562</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>DOMINGBO</t>
+        </is>
+      </c>
+      <c r="O84" s="6" t="inlineStr">
+        <is>
+          <t>AGNAN RAOUL</t>
+        </is>
+      </c>
+      <c r="P84" s="6" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>ZONA ROLD</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>AZON</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>PASTEL ROLANDO</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>2290166335562</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>AZON</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>PASTEL ROLANDO</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>2290166335562</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>DOMINGBO</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
+          <t>AGNAN RAOUL</t>
+        </is>
+      </c>
+      <c r="P85" s="6" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>ZONA ROLD</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>AZON</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>PASTEL ROLANDO</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>2290166335562</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>AZON</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>PASTEL ROLANDO</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>2290166335562</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N86" s="6" t="inlineStr">
+        <is>
+          <t>DOMINGBO</t>
+        </is>
+      </c>
+      <c r="O86" s="6" t="inlineStr">
+        <is>
+          <t>AGNAN RAOUL</t>
+        </is>
+      </c>
+      <c r="P86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>ZOTCHEZE MAWUENA</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>TOSSOU</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>SEFACON SABINE</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>2290129607964</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>TOSSOU</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>SEFACON SABINE</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>2290129607964</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>PRODUITS GSM</t>
+        </is>
+      </c>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N87" s="6" t="inlineStr">
+        <is>
+          <t>AIWEME</t>
+        </is>
+      </c>
+      <c r="O87" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P87" s="6" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>BRUNO ATTE SERVICE PLUS</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>TOTIN</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>BRUNO</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>2290162616312</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>TOTIN</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>BRUNO</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>2290162616312</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N88" s="6" t="inlineStr">
+        <is>
+          <t>ZOUNGO</t>
+        </is>
+      </c>
+      <c r="O88" s="6" t="inlineStr">
+        <is>
+          <t>SOUNOUVOU FLORENT</t>
+        </is>
+      </c>
+      <c r="P88" s="6" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>CANONKO SERVICES ET FILS</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>ANONKO</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>CYPRIEN</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>2290169487881</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>ANONKO</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>CYPRIEN</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>2290169487881</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>COUFFO</t>
+        </is>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>TOVIKLIN</t>
+        </is>
+      </c>
+      <c r="N89" s="6" t="inlineStr">
+        <is>
+          <t>CENTRE</t>
+        </is>
+      </c>
+      <c r="O89" s="6" t="inlineStr">
+        <is>
+          <t>TAGNON ANCE</t>
+        </is>
+      </c>
+      <c r="P89" s="6" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>CHEZ KAWA</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>OSSAH</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>MATHIEU HOUNKONNOU</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>2290197561310</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>OSSAH</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>MATHIEU HOUNKONNOU</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>2290197561310</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>PRODUITS GSM</t>
+        </is>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY</t>
+        </is>
+      </c>
+      <c r="N90" s="6" t="inlineStr">
+        <is>
+          <t>DJEGBE</t>
+        </is>
+      </c>
+      <c r="O90" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P90" s="6" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>CHEZ KPADONOU</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>KPADONOU</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>ESPERA PROSPERE</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>2290153666793</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>KPADONOU</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>ESPERA PROSPERE</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>2290153666793</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>COMMUNICATION, COMPLÉMENTS ALIMENTAIRES</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>NATITINGOU</t>
+        </is>
+      </c>
+      <c r="N91" s="6" t="inlineStr">
+        <is>
+          <t>OURBOUGA</t>
+        </is>
+      </c>
+      <c r="O91" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P91" s="6" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>CHRIST ELU</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>AZANMANVO</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>DINO JUNIOR AQUILAS</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>2290197837909</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>AZANMANVO</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>DINO JUNIOR AQUILAS</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>2290197837909</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>PRODUITS GSM</t>
+        </is>
+      </c>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY</t>
+        </is>
+      </c>
+      <c r="N92" s="6" t="inlineStr">
+        <is>
+          <t>ZOUNZONME</t>
+        </is>
+      </c>
+      <c r="O92" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P92" s="6" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>D BENIOLE SERVICE</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>DEHOKIN</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>MIDOKPE AURIOLE BERNICE</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>2290158250150</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>DEHOKIN</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>MIDOKPE AURIOLE BERNICE</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>2290158250150</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>PRESTATION</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N93" s="6" t="inlineStr">
+        <is>
+          <t>ZOUNGOUDO</t>
+        </is>
+      </c>
+      <c r="O93" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P93" s="6" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>DADJO WENCE ETS FILS</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>DADJO</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>COISSI WENCESLAS</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>2290166385460</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>DADJO</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>COISSI WENCESLAS</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>2290166385460</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>COVÈ</t>
+        </is>
+      </c>
+      <c r="N94" s="6" t="inlineStr">
+        <is>
+          <t>AGA</t>
+        </is>
+      </c>
+      <c r="O94" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P94" s="6" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>DAGAPA ET FILS</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>DAGAPA</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>NAWAN JOSOUE</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>2290167333345</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>DAGAPA</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>NAWAN JOSOUE</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>2290167333345</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>USTENSILES DE CUISINES</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>TOUCOUNTOUNA</t>
+        </is>
+      </c>
+      <c r="N95" s="6" t="inlineStr">
+        <is>
+          <t>KPENTIKOU</t>
+        </is>
+      </c>
+      <c r="O95" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P95" s="6" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>DEEN IGWE SERVICES</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>AHISSOUVOU</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>YENOUKOUNME FERDINAND</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>2290169536066</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>AHISSOUVOU</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>YENOUKOUNME FERDINAND</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>2290169536066</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>BIJOUTERIE JOAILLERIE</t>
+        </is>
+      </c>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N96" s="6" t="inlineStr">
+        <is>
+          <t>AKOSSANIE</t>
+        </is>
+      </c>
+      <c r="O96" s="6" t="inlineStr">
+        <is>
+          <t>SOUNOUVOU FLORENT</t>
+        </is>
+      </c>
+      <c r="P96" s="6" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>DGB MOMO</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>DAGLANON</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>GILBERTE BELMONDE</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>2290162793902</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>DAGLANON</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>GILBERTE BELMONDE</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>2290162793902</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N97" s="6" t="inlineStr">
+        <is>
+          <t>TANKPE</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
+          <t>MELE PRINCE</t>
+        </is>
+      </c>
+      <c r="P97" s="6" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>DHOSSOU ET FILS</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>DHOSSOU</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>KOCOUVI JEAN</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>2290164485258</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>DHOSSOU</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>KOCOUVI JEAN</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>2290164485258</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>COUFFO</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>KLOUÉKANMÈ</t>
+        </is>
+      </c>
+      <c r="N98" s="6" t="inlineStr">
+        <is>
+          <t>LANTA</t>
+        </is>
+      </c>
+      <c r="O98" s="6" t="inlineStr">
+        <is>
+          <t>TAGNON ANCE</t>
+        </is>
+      </c>
+      <c r="P98" s="6" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>DIBO VIBES</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>GANLAKI</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>JUNIOR-DIBO</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>2290164177178</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>GANLAKI</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>JUNIOR-DIBO</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>2290164177178</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>PRESTATIONS DE SERVICES</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N99" s="6" t="inlineStr">
+        <is>
+          <t>AHOSSOU GBETA</t>
+        </is>
+      </c>
+      <c r="O99" s="6" t="inlineStr">
+        <is>
+          <t>CHICOTO EVRARD</t>
+        </is>
+      </c>
+      <c r="P99" s="6" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>DJROTIN ET FILS</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>BEKPA KINHOU</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>IGNACE</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>2290161283827</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>BEKPA KINHOU</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>IGNACE</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>2290161283827</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>COUFFO</t>
+        </is>
+      </c>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>KLOUÉKANMÈ</t>
+        </is>
+      </c>
+      <c r="N100" s="6" t="inlineStr">
+        <is>
+          <t>CENTRE</t>
+        </is>
+      </c>
+      <c r="O100" s="6" t="inlineStr">
+        <is>
+          <t>TAGNON ANCE</t>
+        </is>
+      </c>
+      <c r="P100" s="6" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>DOSSI AGONMAN ET FILS</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>AGONMAN</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>JOSEPHINE</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>2290194757305</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>AGONMAN</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>JOSEPHINE</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>2290194757305</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>VENTE DE FOURNITURE SCOLAIRE EN GROS</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N101" s="6" t="inlineStr">
+        <is>
+          <t>OUEDO</t>
+        </is>
+      </c>
+      <c r="O101" s="6" t="inlineStr">
+        <is>
+          <t>SALIGA THIERIE</t>
+        </is>
+      </c>
+      <c r="P101" s="6" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>DOUCEUR HOUESSOU ET FILS</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>HOUESSOU</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>MAHUSSI MARTHE AKPEDJE</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>2290150236930</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>HOUESSOU</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>MAHUSSI MARTHE AKPEDJE</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>2290150236930</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>PAPETERIE</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M102" s="6" t="inlineStr">
+        <is>
+          <t>COBLY</t>
+        </is>
+      </c>
+      <c r="N102" s="6" t="inlineStr">
+        <is>
+          <t>COBLY</t>
+        </is>
+      </c>
+      <c r="O102" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P102" s="6" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>ESDRACE ET FILS</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>M'PO MOUYORE</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>KOUAGOU ESDRACE</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>2290191097640</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>M'PO MOUYORE</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>KOUAGOU ESDRACE</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>2290191097640</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>PRÊT À PORTER</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>TOUCOUNTOUNA</t>
+        </is>
+      </c>
+      <c r="N103" s="6" t="inlineStr">
+        <is>
+          <t>TAMPÉGNÉ</t>
+        </is>
+      </c>
+      <c r="O103" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P103" s="6" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>ETS AVALOU</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>DJENONTIN</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>ROCK NARCISSE</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>2290195459495</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>DJENONTIN</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>ROCK NARCISSE</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>2290195459495</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>VENTE DE PRODUITS SOBEBRA</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>COVÈ</t>
+        </is>
+      </c>
+      <c r="N104" s="6" t="inlineStr">
+        <is>
+          <t>DOME</t>
+        </is>
+      </c>
+      <c r="O104" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P104" s="6" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>FENOU DAV</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>DJIDAGO</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>TODATCHE DAVID</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>2290165264120</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>DJIDAGO</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>TODATCHE DAVID</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>2290165264120</t>
+        </is>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>ALIMENTATION GENERALE</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N105" s="6" t="inlineStr">
+        <is>
+          <t>ADOVIE</t>
+        </is>
+      </c>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
+          <t>SOUNOUVOU FLORENT</t>
+        </is>
+      </c>
+      <c r="P105" s="6" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>FIDELITE SERVICE MAHOUGNON</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>ZANNOU</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>FIDÈLE</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>2290141520629</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>ZANNOU</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>FIDÈLE</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>2290141520629</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M106" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N106" s="6" t="inlineStr">
+        <is>
+          <t>WEDJI</t>
+        </is>
+      </c>
+      <c r="O106" s="6" t="inlineStr">
+        <is>
+          <t>AGNAN RAOUL</t>
+        </is>
+      </c>
+      <c r="P106" s="6" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>FOLAKEMI TWINS ET FILS</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>ADEFALOU</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>FOLAKEMI GEORGETTE</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>2290197580602</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>ADEFALOU</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>FOLAKEMI GEORGETTE</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>2290197580602</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M107" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY</t>
+        </is>
+      </c>
+      <c r="N107" s="6" t="inlineStr">
+        <is>
+          <t>ZOUNAONHE</t>
+        </is>
+      </c>
+      <c r="O107" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P107" s="6" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>GIL KEL ET FILS</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>KLOMONDE</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>GILDAS</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>2290195221543</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>KLOMONDE</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>GILDAS</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>2290195221543</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>COUFFO</t>
+        </is>
+      </c>
+      <c r="M108" s="6" t="inlineStr">
+        <is>
+          <t>DJAKOTOMEY</t>
+        </is>
+      </c>
+      <c r="N108" s="6" t="inlineStr">
+        <is>
+          <t>CENTRE</t>
+        </is>
+      </c>
+      <c r="O108" s="6" t="inlineStr">
+        <is>
+          <t>TAGNON ANCE</t>
+        </is>
+      </c>
+      <c r="P108" s="6" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>GYSTORE</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>GUEDEME</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>YEYI</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>2290161523246</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>GUEDEME</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>YEYI</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>2290161523246</t>
+        </is>
+      </c>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>VENTE D'APPAREILS ELECTRO-MENAGERS</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N109" s="6" t="inlineStr">
+        <is>
+          <t>HONMEHO</t>
+        </is>
+      </c>
+      <c r="O109" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P109" s="6" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>HORIZON BEL</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>AGBESSI</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>BELMONDO DEGLA DEWANOU</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>2290152560353</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>AGBESSI</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>BELMONDO DEGLA DEWANOU</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>2290152560353</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>RESTAURANT</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M110" s="6" t="inlineStr">
+        <is>
+          <t>KÉROU</t>
+        </is>
+      </c>
+      <c r="N110" s="6" t="inlineStr">
+        <is>
+          <t>KEROU-WIROU</t>
+        </is>
+      </c>
+      <c r="O110" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P110" s="6" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>HOSANNA SPACES CONSULTING</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>DOGBALIE</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>ERNEST</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>2290167169660</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>DOGBALIE</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>ERNEST</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>2290167169660</t>
+        </is>
+      </c>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N111" s="6" t="inlineStr">
+        <is>
+          <t>ZOGBAGJE</t>
+        </is>
+      </c>
+      <c r="O111" s="6" t="inlineStr">
+        <is>
+          <t>MELE PRINCE</t>
+        </is>
+      </c>
+      <c r="P111" s="6" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>HOUMABOU DIEU EST LA SOLUTION</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>SETONON</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>HOUMABOU DIEU-DONNÉ</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>2290195993201</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>SETONON</t>
+        </is>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>HOUMABOU DIEU-DONNÉ</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>2290195993201</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>VENTE DE PORTABLES</t>
+        </is>
+      </c>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M112" s="6" t="inlineStr">
+        <is>
+          <t>ZAGNANADO</t>
+        </is>
+      </c>
+      <c r="N112" s="6" t="inlineStr">
+        <is>
+          <t>HOUEGBO AGA</t>
+        </is>
+      </c>
+      <c r="O112" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P112" s="6" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>JAUPAR</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>SOBAKPO</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>BIGNON ORLAND JAURES</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>2290166520688</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>SOBAKPO</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>BIGNON ORLAND JAURES</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>2290166520688</t>
+        </is>
+      </c>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>BTP</t>
+        </is>
+      </c>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY</t>
+        </is>
+      </c>
+      <c r="N113" s="6" t="inlineStr">
+        <is>
+          <t>ZOUNZONME</t>
+        </is>
+      </c>
+      <c r="O113" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P113" s="6" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>JC EVOLASS</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>TOGNON</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>COSSI JOHANN</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>2290165968304</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>TOGNON</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>COSSI JOHANN</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>2290165968304</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>ACHAT ET VENTE DE TELEPHONE</t>
+        </is>
+      </c>
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M114" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N114" s="6" t="inlineStr">
+        <is>
+          <t>ADJAKBO</t>
+        </is>
+      </c>
+      <c r="O114" s="6" t="inlineStr">
+        <is>
+          <t>ODOH ARCHANGE</t>
+        </is>
+      </c>
+      <c r="P114" s="6" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>JESU DOHAMI SERVICE</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>MIADINOU</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>VALENTIN</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>2290162276319</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>MIADINOU</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>VALENTIN</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>2290162276319</t>
+        </is>
+      </c>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>COUFFO</t>
+        </is>
+      </c>
+      <c r="M115" s="6" t="inlineStr">
+        <is>
+          <t>APLAHOUÉ</t>
+        </is>
+      </c>
+      <c r="N115" s="6" t="inlineStr">
+        <is>
+          <t>AZOVE</t>
+        </is>
+      </c>
+      <c r="O115" s="6" t="inlineStr">
+        <is>
+          <t>TAGNON ANCE</t>
+        </is>
+      </c>
+      <c r="P115" s="6" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>JLOMAHOUTON COIFFURE</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>DASSI</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>FRANCK</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>2290194962766</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>DASSI</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>FRANCK</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>2290194962766</t>
+        </is>
+      </c>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>VENTE DE CIMENT / COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L116" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M116" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N116" s="6" t="inlineStr">
+        <is>
+          <t>YEKONAGA</t>
+        </is>
+      </c>
+      <c r="O116" s="6" t="inlineStr">
+        <is>
+          <t>AGNAN RAOUL</t>
+        </is>
+      </c>
+      <c r="P116" s="6" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>KDEJ SERVICES</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>DADAVI</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>PASCALINE</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>2290197454428</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>DADAVI</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>PASCALINE</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>2290197454428</t>
+        </is>
+      </c>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>PRODUITS GSM</t>
+        </is>
+      </c>
+      <c r="L117" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M117" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N117" s="6" t="inlineStr">
+        <is>
+          <t>ZOUNGOUDO</t>
+        </is>
+      </c>
+      <c r="O117" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P117" s="6" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>KINWOU ET FILS</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>LEGBA</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>KINWOU FLORENT</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>2290196097303</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>LEGBA</t>
+        </is>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>KINWOU FLORENT</t>
+        </is>
+      </c>
+      <c r="J118" s="6" t="inlineStr">
+        <is>
+          <t>2290196097303</t>
+        </is>
+      </c>
+      <c r="K118" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L118" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M118" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N118" s="6" t="inlineStr">
+        <is>
+          <t>GLEGBODJI</t>
+        </is>
+      </c>
+      <c r="O118" s="6" t="inlineStr">
+        <is>
+          <t>AGNAN RAOUL</t>
+        </is>
+      </c>
+      <c r="P118" s="6" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>KINWOU ET FILS</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>LEGBA</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>KINWOU FLORENT</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>2290196097303</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>LEGBA</t>
+        </is>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>KINWOU FLORENT</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>2290196097303</t>
+        </is>
+      </c>
+      <c r="K119" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L119" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M119" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N119" s="6" t="inlineStr">
+        <is>
+          <t>GLEGBODJI</t>
+        </is>
+      </c>
+      <c r="O119" s="6" t="inlineStr">
+        <is>
+          <t>AGNAN RAOUL</t>
+        </is>
+      </c>
+      <c r="P119" s="6" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>KOYAAH ET FILS</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>KOYI</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>ENAGNON EDWIGE</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>2290169021455</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>KOYI</t>
+        </is>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>ENAGNON EDWIGE</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="inlineStr">
+        <is>
+          <t>2290169021455</t>
+        </is>
+      </c>
+      <c r="K120" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L120" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M120" s="6" t="inlineStr">
+        <is>
+          <t>HELITA</t>
+        </is>
+      </c>
+      <c r="N120" s="6" t="inlineStr">
+        <is>
+          <t>HELITA</t>
+        </is>
+      </c>
+      <c r="O120" s="6" t="inlineStr">
+        <is>
+          <t>MOUZOUN HONORÉ</t>
+        </is>
+      </c>
+      <c r="P120" s="6" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>LA FLECHE DU NORD</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>BAMPO</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>AUGUSTIN</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>2290166732759</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>BAMPO</t>
+        </is>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>AUGUSTIN</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="inlineStr">
+        <is>
+          <t>2290166732759</t>
+        </is>
+      </c>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>IMMOBILIER</t>
+        </is>
+      </c>
+      <c r="L121" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M121" s="6" t="inlineStr">
+        <is>
+          <t>NATITINGOU</t>
+        </is>
+      </c>
+      <c r="N121" s="6" t="inlineStr">
+        <is>
+          <t>OUROUBONNA</t>
+        </is>
+      </c>
+      <c r="O121" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P121" s="6" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>LA JOIE DE FIROU ET FILS</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>DHOSSOUVI</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>ALPHONSE</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>2290160207498</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>DHOSSOUVI</t>
+        </is>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>ALPHONSE</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="inlineStr">
+        <is>
+          <t>2290160207498</t>
+        </is>
+      </c>
+      <c r="K122" s="6" t="inlineStr">
+        <is>
+          <t>ALIMENTATION GÉNÉRALE</t>
+        </is>
+      </c>
+      <c r="L122" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M122" s="6" t="inlineStr">
+        <is>
+          <t>KÉROU</t>
+        </is>
+      </c>
+      <c r="N122" s="6" t="inlineStr">
+        <is>
+          <t>FIROU</t>
+        </is>
+      </c>
+      <c r="O122" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P122" s="6" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>LA MAIN DE DIEU HKB</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>KEDEKE</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>BEMAS</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>2290167460884</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>KEDEKE</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>BEMAS</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>2290167460884</t>
+        </is>
+      </c>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>QUINCALLERIE</t>
+        </is>
+      </c>
+      <c r="L123" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M123" s="6" t="inlineStr">
+        <is>
+          <t>OUIDAH</t>
+        </is>
+      </c>
+      <c r="N123" s="6" t="inlineStr">
+        <is>
+          <t>ADJRA-HOUNVÈ</t>
+        </is>
+      </c>
+      <c r="O123" s="6" t="inlineStr">
+        <is>
+          <t>ERIC PADONOU</t>
+        </is>
+      </c>
+      <c r="P123" s="6" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>LA MAIN DU PERE</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>ADOKINTO</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>ERIC</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>2290194812951</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>ADOKINTO</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>ERIC</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
+          <t>2290194812951</t>
+        </is>
+      </c>
+      <c r="K124" s="6" t="inlineStr">
+        <is>
+          <t>PRET A PORTER</t>
+        </is>
+      </c>
+      <c r="L124" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M124" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N124" s="6" t="inlineStr">
+        <is>
+          <t>AKOSSAVIE</t>
+        </is>
+      </c>
+      <c r="O124" s="6" t="inlineStr">
+        <is>
+          <t>SOUNOUVOU FLORENT</t>
+        </is>
+      </c>
+      <c r="P124" s="6" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>LA FERME DE LAGRICULTRICE</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>KONSAGOU</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>NADEGE</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>2290197965773</t>
+        </is>
+      </c>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>KONSAGOU</t>
+        </is>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>NADEGE</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr">
+        <is>
+          <t>2290197965773</t>
+        </is>
+      </c>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>FERME AGRICOLE</t>
+        </is>
+      </c>
+      <c r="L125" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M125" s="6" t="inlineStr">
+        <is>
+          <t>NATITINGOU</t>
+        </is>
+      </c>
+      <c r="N125" s="6" t="inlineStr">
+        <is>
+          <t>WINKÉ</t>
+        </is>
+      </c>
+      <c r="O125" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P125" s="6" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>ENERGIE PLUS BTP</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>MADOUGOU</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>IDRISSOU</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>2290195269586</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>MADOUGOU</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>IDRISSOU</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="inlineStr">
+        <is>
+          <t>2290195269586</t>
+        </is>
+      </c>
+      <c r="K126" s="6" t="inlineStr">
+        <is>
+          <t>ELECTRICITE BATIMENT</t>
+        </is>
+      </c>
+      <c r="L126" s="6" t="inlineStr">
+        <is>
+          <t>ATLANTIQUE</t>
+        </is>
+      </c>
+      <c r="M126" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY-CALAVI</t>
+        </is>
+      </c>
+      <c r="N126" s="6" t="inlineStr">
+        <is>
+          <t>ADJAGBO</t>
+        </is>
+      </c>
+      <c r="O126" s="6" t="inlineStr">
+        <is>
+          <t>ODOH ARCHANGE</t>
+        </is>
+      </c>
+      <c r="P126" s="6" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>ADELPHOS</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>GOUSSI</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>ADELPHE KOFFI</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>2290196697603</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>GOUSSI</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>ADELPHE KOFFI</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>2290196697603</t>
+        </is>
+      </c>
+      <c r="K127" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L127" s="6" t="inlineStr">
+        <is>
+          <t>COUFFO</t>
+        </is>
+      </c>
+      <c r="M127" s="6" t="inlineStr">
+        <is>
+          <t>DJAKOTOMEY</t>
+        </is>
+      </c>
+      <c r="N127" s="6" t="inlineStr">
+        <is>
+          <t>CENTRE</t>
+        </is>
+      </c>
+      <c r="O127" s="6" t="inlineStr">
+        <is>
+          <t>TAGNON ANCE</t>
+        </is>
+      </c>
+      <c r="P127" s="6" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>ADIHA ET FILS</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>ADIHA</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>PAUL</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>2290164507807</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>ADIHA</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>PAUL</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr">
+        <is>
+          <t>2290164507807</t>
+        </is>
+      </c>
+      <c r="K128" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L128" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M128" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N128" s="6" t="inlineStr">
+        <is>
+          <t>KPOCON</t>
+        </is>
+      </c>
+      <c r="O128" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P128" s="6" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>ADIHA ET FILS</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>ADIHA</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>PAUL</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>2290164507807</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>ADIHA</t>
+        </is>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>PAUL</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="inlineStr">
+        <is>
+          <t>2290164507807</t>
+        </is>
+      </c>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>QUINCAILLERIE</t>
+        </is>
+      </c>
+      <c r="L129" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M129" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N129" s="6" t="inlineStr">
+        <is>
+          <t>ADAME AHITO</t>
+        </is>
+      </c>
+      <c r="O129" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P129" s="6" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>ADOMAHOUTO SERVICES</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>SOGLO</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>ROMAIN</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>2290195799817</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>SOGLO</t>
+        </is>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>ROMAIN</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="inlineStr">
+        <is>
+          <t>2290195799817</t>
+        </is>
+      </c>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>BTP</t>
+        </is>
+      </c>
+      <c r="L130" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M130" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N130" s="6" t="inlineStr">
+        <is>
+          <t>ADAME-AHITO</t>
+        </is>
+      </c>
+      <c r="O130" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P130" s="6" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>AGLA ET FILS</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>AGLA</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>JOEL</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>2290198250049</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>AGLA</t>
+        </is>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>JOEL</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="inlineStr">
+        <is>
+          <t>2290198250049</t>
+        </is>
+      </c>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>PRÊT À PORTER</t>
+        </is>
+      </c>
+      <c r="L131" s="6" t="inlineStr">
+        <is>
+          <t>MONO</t>
+        </is>
+      </c>
+      <c r="M131" s="6" t="inlineStr">
+        <is>
+          <t>HOUÉYOGBÉ</t>
+        </is>
+      </c>
+      <c r="N131" s="6" t="inlineStr">
+        <is>
+          <t>HONHOUE</t>
+        </is>
+      </c>
+      <c r="O131" s="6" t="inlineStr">
+        <is>
+          <t>KAKPOVI SEBASTIEN</t>
+        </is>
+      </c>
+      <c r="P131" s="6" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>AGOLINOU ET FILS</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>AGOLINOU</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>OSCAR QUEMAMBEL</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>2290190775110</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>AGOLINOU</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>OSCAR QUEMAMBEL</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>2290190775110</t>
+        </is>
+      </c>
+      <c r="K132" s="6" t="inlineStr">
+        <is>
+          <t>PRODUITS GSM</t>
+        </is>
+      </c>
+      <c r="L132" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M132" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N132" s="6" t="inlineStr">
+        <is>
+          <t>AGONVEZOUN</t>
+        </is>
+      </c>
+      <c r="O132" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P132" s="6" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>AMOUR AMOUR AMOUR SERVICES</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>ADAGBE</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>ZOHOUNGUIDA HONORINE</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>2290197023792</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>ADAGBE</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>ZOHOUNGUIDA HONORINE</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>2290197023792</t>
+        </is>
+      </c>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L133" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M133" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N133" s="6" t="inlineStr">
+        <is>
+          <t>HONHEHO</t>
+        </is>
+      </c>
+      <c r="O133" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P133" s="6" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>AMOUR AMOUR AMOUR SERVICES</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>ADAGBE</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>ZOHOUNGUIDA HONORINE</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>2290197023792</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>ADAGBE</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>ZOHOUNGUIDA HONORINE</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="inlineStr">
+        <is>
+          <t>2290197023792</t>
+        </is>
+      </c>
+      <c r="K134" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L134" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M134" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N134" s="6" t="inlineStr">
+        <is>
+          <t>SEYONDJI</t>
+        </is>
+      </c>
+      <c r="O134" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P134" s="6" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>AYIFFON</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>DAGBEDE</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>TOGNISSOU HABIB</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>2290140042739</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>DAGBEDE</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>TOGNISSOU HABIB</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>2290140042739</t>
+        </is>
+      </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>CUISINE</t>
+        </is>
+      </c>
+      <c r="L135" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M135" s="6" t="inlineStr">
+        <is>
+          <t>NATITINGOU</t>
+        </is>
+      </c>
+      <c r="N135" s="6" t="inlineStr">
+        <is>
+          <t>YOKOSSI</t>
+        </is>
+      </c>
+      <c r="O135" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P135" s="6" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>ANGEL FINGERS EVENT</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>HADJETE</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>HERMIGNONNE LOUISE</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>2290146227730</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>HADJETE</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>HERMIGNONNE LOUISE</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="inlineStr">
+        <is>
+          <t>2290146227730</t>
+        </is>
+      </c>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GÉNÉRALE</t>
+        </is>
+      </c>
+      <c r="L136" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M136" s="6" t="inlineStr">
+        <is>
+          <t>MATÉRI</t>
+        </is>
+      </c>
+      <c r="N136" s="6" t="inlineStr">
+        <is>
+          <t>MATÉRI</t>
+        </is>
+      </c>
+      <c r="O136" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P136" s="6" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>BOOMI</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>TCHOROMI</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>TCHOROPA TANGUY</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>2290161195321</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>TCHOROMI</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>TCHOROPA TANGUY</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>2290161195321</t>
+        </is>
+      </c>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t>BAR-RESTAURANT</t>
+        </is>
+      </c>
+      <c r="L137" s="6" t="inlineStr">
+        <is>
+          <t>ATACORA</t>
+        </is>
+      </c>
+      <c r="M137" s="6" t="inlineStr">
+        <is>
+          <t>NATITINGOU</t>
+        </is>
+      </c>
+      <c r="N137" s="6" t="inlineStr">
+        <is>
+          <t>TCHIRIMING</t>
+        </is>
+      </c>
+      <c r="O137" s="6" t="inlineStr">
+        <is>
+          <t>AWO BERNADIN</t>
+        </is>
+      </c>
+      <c r="P137" s="6" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>CHEZ MAX LOLO</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>AGBESSI</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>SEDJOLO HANS TIBUS</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>2290169599964</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>AGBESSI</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>SEDJOLO HANS TIBUS</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>2290169599964</t>
+        </is>
+      </c>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L138" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M138" s="6" t="inlineStr">
+        <is>
+          <t>ABOMEY</t>
+        </is>
+      </c>
+      <c r="N138" s="6" t="inlineStr">
+        <is>
+          <t>DJEGBE</t>
+        </is>
+      </c>
+      <c r="O138" s="6" t="inlineStr">
+        <is>
+          <t>BERNARD DOVONOU</t>
+        </is>
+      </c>
+      <c r="P138" s="6" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>CHRIST GENIAL</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>DANHOUNDO</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>MAHUGNON MODESTE FIDEL</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>2290164777756</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>DANHOUNDO</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>MAHUGNON MODESTE FIDEL</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t>2290164777756</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCE GENERAL</t>
+        </is>
+      </c>
+      <c r="L139" s="6" t="inlineStr">
+        <is>
+          <t>ZOU</t>
+        </is>
+      </c>
+      <c r="M139" s="6" t="inlineStr">
+        <is>
+          <t>BOHICON</t>
+        </is>
+      </c>
+      <c r="N139" s="6" t="inlineStr">
+        <is>
+          <t>ZAKPOADAGAME</t>
+        </is>
+      </c>
+      <c r="O139" s="6" t="inlineStr">
+        <is>
+          <t>ILLO WABI AMADOU</t>
+        </is>
+      </c>
+      <c r="P139" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
